--- a/site/assets/examples/06-create-a-chart.xlsx
+++ b/site/assets/examples/06-create-a-chart.xlsx
@@ -188,6 +188,11 @@
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
